--- a/5/search/FY5_Missile1_results/fine_tuned/top10_fine_tuned_solutions.xlsx
+++ b/5/search/FY5_Missile1_results/fine_tuned/top10_fine_tuned_solutions.xlsx
@@ -492,227 +492,227 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131</v>
+        <v>94.8</v>
       </c>
       <c r="B2" t="n">
-        <v>126.3</v>
+        <v>99.8</v>
       </c>
       <c r="C2" t="n">
-        <v>15.4</v>
+        <v>18.8</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8</v>
+        <v>1.4</v>
       </c>
       <c r="E2" t="n">
-        <v>11723.95206743288</v>
+        <v>12843.00028322618</v>
       </c>
       <c r="F2" t="n">
-        <v>-532.0747722751037</v>
+        <v>-130.3402377617099</v>
       </c>
       <c r="G2" t="n">
         <v>1300</v>
       </c>
       <c r="H2" t="n">
-        <v>11243.36258633618</v>
+        <v>12831.30881495578</v>
       </c>
       <c r="I2" t="n">
-        <v>20.7801836212858</v>
+        <v>8.889744532630715</v>
       </c>
       <c r="J2" t="n">
-        <v>1135.164</v>
+        <v>1290.396</v>
       </c>
       <c r="K2" t="n">
-        <v>3.600000000000001</v>
+        <v>3.800000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122</v>
+        <v>94.8</v>
       </c>
       <c r="B3" t="n">
-        <v>120.1</v>
+        <v>102.8</v>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>18.2</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="E3" t="n">
-        <v>12045.35044548388</v>
+        <v>12843.44210223897</v>
       </c>
       <c r="F3" t="n">
-        <v>-472.2413547741985</v>
+        <v>-135.6017200585472</v>
       </c>
       <c r="G3" t="n">
         <v>1300</v>
       </c>
       <c r="H3" t="n">
-        <v>11739.86258803872</v>
+        <v>12831.39918702658</v>
       </c>
       <c r="I3" t="n">
-        <v>16.64141169805805</v>
+        <v>7.813532244641294</v>
       </c>
       <c r="J3" t="n">
-        <v>1187.104</v>
+        <v>1290.396</v>
       </c>
       <c r="K3" t="n">
-        <v>3.600000000000001</v>
+        <v>3.800000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="B4" t="n">
-        <v>120.1</v>
+        <v>105.8</v>
       </c>
       <c r="C4" t="n">
-        <v>15.4</v>
+        <v>18.8</v>
       </c>
       <c r="D4" t="n">
-        <v>5.2</v>
+        <v>0.2</v>
       </c>
       <c r="E4" t="n">
-        <v>11933.86537395132</v>
+        <v>12944.46274371327</v>
       </c>
       <c r="F4" t="n">
-        <v>-488.6578247332463</v>
+        <v>-11.73549678013364</v>
       </c>
       <c r="G4" t="n">
         <v>1300</v>
       </c>
       <c r="H4" t="n">
-        <v>11573.87186385696</v>
+        <v>12943.87192183788</v>
       </c>
       <c r="I4" t="n">
-        <v>21.66550717500826</v>
+        <v>9.416253254120178</v>
       </c>
       <c r="J4" t="n">
-        <v>1167.504</v>
+        <v>1299.804</v>
       </c>
       <c r="K4" t="n">
-        <v>3.600000000000001</v>
+        <v>3.800000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128.4</v>
+        <v>94.8</v>
       </c>
       <c r="B5" t="n">
-        <v>116.1</v>
+        <v>101.8</v>
       </c>
       <c r="C5" t="n">
-        <v>16.6</v>
+        <v>18.2</v>
       </c>
       <c r="D5" t="n">
-        <v>5.6</v>
+        <v>1.6</v>
       </c>
       <c r="E5" t="n">
-        <v>11802.88672898082</v>
+        <v>12844.96503898762</v>
       </c>
       <c r="F5" t="n">
-        <v>-489.6189474342018</v>
+        <v>-153.7378900968883</v>
       </c>
       <c r="G5" t="n">
         <v>1300</v>
       </c>
       <c r="H5" t="n">
-        <v>11399.04128815508</v>
+        <v>12831.33559186565</v>
       </c>
       <c r="I5" t="n">
-        <v>19.90719078076631</v>
+        <v>8.57086681767106</v>
       </c>
       <c r="J5" t="n">
-        <v>1146.336</v>
+        <v>1287.456</v>
       </c>
       <c r="K5" t="n">
-        <v>3.599999999999998</v>
+        <v>3.700000000000003</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137.4</v>
+        <v>93.2</v>
       </c>
       <c r="B6" t="n">
-        <v>131.3</v>
+        <v>102.8</v>
       </c>
       <c r="C6" t="n">
-        <v>16.2</v>
+        <v>18.8</v>
       </c>
       <c r="D6" t="n">
-        <v>6.6</v>
+        <v>0.8</v>
       </c>
       <c r="E6" t="n">
-        <v>11434.2773298711</v>
+        <v>12892.11712659001</v>
       </c>
       <c r="F6" t="n">
-        <v>-560.2441999267996</v>
+        <v>-70.37344151133607</v>
       </c>
       <c r="G6" t="n">
         <v>1300</v>
       </c>
       <c r="H6" t="n">
-        <v>10796.39031611488</v>
+        <v>12887.52636601937</v>
       </c>
       <c r="I6" t="n">
-        <v>26.32297788080041</v>
+        <v>11.73832693499013</v>
       </c>
       <c r="J6" t="n">
-        <v>1086.556</v>
+        <v>1296.864</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5</v>
+        <v>3.699999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>90.8</v>
+        <v>93.2</v>
       </c>
       <c r="B7" t="n">
-        <v>101.3</v>
+        <v>103.8</v>
       </c>
       <c r="C7" t="n">
-        <v>19.8</v>
+        <v>18.2</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="E7" t="n">
-        <v>12971.99549640656</v>
+        <v>12894.54424562711</v>
       </c>
       <c r="F7" t="n">
-        <v>5.544488506421885</v>
+        <v>-113.7856459379689</v>
       </c>
       <c r="G7" t="n">
         <v>1300</v>
       </c>
       <c r="H7" t="n">
-        <v>12971.99549640656</v>
+        <v>12887.59111896517</v>
       </c>
       <c r="I7" t="n">
-        <v>5.544488506421885</v>
+        <v>10.58013564853862</v>
       </c>
       <c r="J7" t="n">
-        <v>1300</v>
+        <v>1292.944</v>
       </c>
       <c r="K7" t="n">
-        <v>3.5</v>
+        <v>3.699999999999999</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -720,154 +720,154 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="B8" t="n">
-        <v>115.1</v>
+        <v>104.8</v>
       </c>
       <c r="C8" t="n">
-        <v>15.8</v>
+        <v>18.8</v>
       </c>
       <c r="D8" t="n">
-        <v>4.8</v>
+        <v>0.4</v>
       </c>
       <c r="E8" t="n">
-        <v>12036.29942445078</v>
+        <v>12944.98767052128</v>
       </c>
       <c r="F8" t="n">
-        <v>-457.7566932918467</v>
+        <v>-30.52816694289231</v>
       </c>
       <c r="G8" t="n">
         <v>1300</v>
       </c>
       <c r="H8" t="n">
-        <v>11743.52962934722</v>
+        <v>12943.81719542598</v>
       </c>
       <c r="I8" t="n">
-        <v>10.77291887265562</v>
+        <v>11.37548907959919</v>
       </c>
       <c r="J8" t="n">
-        <v>1187.104</v>
+        <v>1299.216</v>
       </c>
       <c r="K8" t="n">
-        <v>3.5</v>
+        <v>3.699999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>90.8</v>
+        <v>122.8</v>
       </c>
       <c r="B9" t="n">
-        <v>100.3</v>
+        <v>121.6</v>
       </c>
       <c r="C9" t="n">
-        <v>19.8</v>
+        <v>14.8</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>12972.27194757728</v>
+        <v>12025.09856811836</v>
       </c>
       <c r="F9" t="n">
-        <v>-14.25358146896224</v>
+        <v>-487.2490950208867</v>
       </c>
       <c r="G9" t="n">
         <v>1300</v>
       </c>
       <c r="H9" t="n">
-        <v>12971.99186623967</v>
+        <v>11695.73997626645</v>
       </c>
       <c r="I9" t="n">
-        <v>5.804463162664334</v>
+        <v>23.81539990448937</v>
       </c>
       <c r="J9" t="n">
-        <v>1299.804</v>
+        <v>1177.5</v>
       </c>
       <c r="K9" t="n">
-        <v>3.5</v>
+        <v>3.699999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130</v>
+        <v>105.4</v>
       </c>
       <c r="B10" t="n">
-        <v>116.1</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>17</v>
+        <v>18.2</v>
       </c>
       <c r="D10" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="E10" t="n">
-        <v>11731.33009476168</v>
+        <v>12529.25398165348</v>
       </c>
       <c r="F10" t="n">
-        <v>-488.0580826160733</v>
+        <v>-290.9673588222777</v>
       </c>
       <c r="G10" t="n">
         <v>1300</v>
       </c>
       <c r="H10" t="n">
-        <v>11313.41530244788</v>
+        <v>12446.4854509552</v>
       </c>
       <c r="I10" t="n">
-        <v>9.993372522161508</v>
+        <v>9.52189676940975</v>
       </c>
       <c r="J10" t="n">
-        <v>1146.336</v>
+        <v>1249.824</v>
       </c>
       <c r="K10" t="n">
-        <v>3.5</v>
+        <v>3.699999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134.2</v>
+        <v>93.2</v>
       </c>
       <c r="B11" t="n">
-        <v>128.3</v>
+        <v>104.8</v>
       </c>
       <c r="C11" t="n">
-        <v>15.8</v>
+        <v>18.8</v>
       </c>
       <c r="D11" t="n">
-        <v>6.2</v>
+        <v>0.4</v>
       </c>
       <c r="E11" t="n">
-        <v>11586.7487333994</v>
+        <v>12890.01823800227</v>
       </c>
       <c r="F11" t="n">
-        <v>-546.7218308074</v>
+        <v>-32.8320687780938</v>
       </c>
       <c r="G11" t="n">
         <v>1300</v>
       </c>
       <c r="H11" t="n">
-        <v>11032.18178068271</v>
+        <v>12887.67820051296</v>
       </c>
       <c r="I11" t="n">
-        <v>23.55188115425312</v>
+        <v>9.022568056414691</v>
       </c>
       <c r="J11" t="n">
-        <v>1111.644</v>
+        <v>1299.216</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5</v>
+        <v>3.699999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
